--- a/fact_inventario/outputs/06_historial_entrenamiento.xlsx
+++ b/fact_inventario/outputs/06_historial_entrenamiento.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1.054250836958312</v>
+        <v>1.054250836958313</v>
       </c>
       <c r="C4" t="n">
         <v>1.044635923165717</v>
@@ -519,7 +519,7 @@
         <v>1.033566394068937</v>
       </c>
       <c r="C6" t="n">
-        <v>1.024348875643652</v>
+        <v>1.024348875643653</v>
       </c>
       <c r="D6" t="n">
         <v>0.7030806647750304</v>
@@ -533,7 +533,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1.023586098862761</v>
+        <v>1.02358609886276</v>
       </c>
       <c r="C7" t="n">
         <v>1.014727477358662</v>
@@ -584,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9960848592108063</v>
+        <v>0.9960848592108064</v>
       </c>
       <c r="C10" t="n">
         <v>0.9884549081385736</v>
@@ -604,7 +604,7 @@
         <v>0.987753785583295</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9804679702499005</v>
+        <v>0.9804679702499006</v>
       </c>
       <c r="D11" t="n">
         <v>0.8754560194568302</v>
@@ -672,7 +672,7 @@
         <v>0.9574306746274009</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9510653844955692</v>
+        <v>0.9510653844955693</v>
       </c>
       <c r="D15" t="n">
         <v>0.9044385893798136</v>
@@ -788,7 +788,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9105279485550194</v>
+        <v>0.9105279485550196</v>
       </c>
       <c r="C22" t="n">
         <v>0.9048910269640402</v>
@@ -859,7 +859,7 @@
         <v>0.8854976627909155</v>
       </c>
       <c r="C26" t="n">
-        <v>0.880114035969807</v>
+        <v>0.8801140359698072</v>
       </c>
       <c r="D26" t="n">
         <v>0.9238954195379003</v>
@@ -893,7 +893,7 @@
         <v>0.8733136232860824</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8680415969893652</v>
+        <v>0.8680415969893653</v>
       </c>
       <c r="D28" t="n">
         <v>0.9247061207944872</v>
@@ -941,7 +941,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8554009266745995</v>
+        <v>0.8554009266745993</v>
       </c>
       <c r="C31" t="n">
         <v>0.8502872345770558</v>
@@ -975,7 +975,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8436875042356886</v>
+        <v>0.8436875042356888</v>
       </c>
       <c r="C33" t="n">
         <v>0.8386761722683528</v>
@@ -992,7 +992,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.8378971308562413</v>
+        <v>0.8378971308562415</v>
       </c>
       <c r="C34" t="n">
         <v>0.8329365096917211</v>
@@ -1094,7 +1094,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.8040634678576941</v>
+        <v>0.8040634678576942</v>
       </c>
       <c r="C40" t="n">
         <v>0.7994062574795375</v>
@@ -1128,7 +1128,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.7931290026684273</v>
+        <v>0.7931290026684275</v>
       </c>
       <c r="C42" t="n">
         <v>0.7885738036040028</v>
@@ -1148,7 +1148,7 @@
         <v>0.7877261294703956</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7832222134456889</v>
+        <v>0.783222213445689</v>
       </c>
       <c r="D43" t="n">
         <v>0.924098094852047</v>
@@ -1162,10 +1162,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.7823662222608245</v>
+        <v>0.7823662222608244</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7779137849666775</v>
+        <v>0.7779137849666776</v>
       </c>
       <c r="D44" t="n">
         <v>0.924098094852047</v>
@@ -1216,7 +1216,7 @@
         <v>0.7665448023005877</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7622479801047316</v>
+        <v>0.7622479801047317</v>
       </c>
       <c r="D47" t="n">
         <v>0.924098094852047</v>
@@ -1298,7 +1298,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>0.7410388077618638</v>
+        <v>0.7410388077618637</v>
       </c>
       <c r="C52" t="n">
         <v>0.73700488191407</v>
@@ -1318,7 +1318,7 @@
         <v>0.7360670775869327</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7320861644237657</v>
+        <v>0.7320861644237658</v>
       </c>
       <c r="D53" t="n">
         <v>0.924098094852047</v>
@@ -1366,7 +1366,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7214098980525989</v>
+        <v>0.721409898052599</v>
       </c>
       <c r="C56" t="n">
         <v>0.7175886562728311</v>
@@ -1400,7 +1400,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>0.711852386154563</v>
+        <v>0.7118523861545631</v>
       </c>
       <c r="C58" t="n">
         <v>0.7081379918660458</v>
@@ -1417,7 +1417,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>0.7071373842062609</v>
+        <v>0.7071373842062608</v>
       </c>
       <c r="C59" t="n">
         <v>0.7034764981444855</v>
@@ -1587,7 +1587,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>0.6622730167689953</v>
+        <v>0.6622730167689954</v>
       </c>
       <c r="C69" t="n">
         <v>0.6591483490225496</v>
@@ -1621,7 +1621,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>0.6537844171243443</v>
+        <v>0.6537844171243444</v>
       </c>
       <c r="C71" t="n">
         <v>0.6507670142181363</v>
@@ -1689,7 +1689,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>0.6372705748384637</v>
+        <v>0.6372705748384636</v>
       </c>
       <c r="C75" t="n">
         <v>0.6344677006308865</v>
@@ -1706,7 +1706,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>0.6332365496444119</v>
+        <v>0.633236549644412</v>
       </c>
       <c r="C76" t="n">
         <v>0.6304873233200113</v>
@@ -1723,7 +1723,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.6292395637271003</v>
+        <v>0.6292395637271002</v>
       </c>
       <c r="C77" t="n">
         <v>0.6265439987124153</v>
@@ -1740,10 +1740,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>0.6252792456130789</v>
+        <v>0.6252792456130791</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6226373593490108</v>
+        <v>0.6226373593490109</v>
       </c>
       <c r="D78" t="n">
         <v>0.9245034454803405</v>
@@ -1757,7 +1757,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>0.6213552228359982</v>
+        <v>0.6213552228359983</v>
       </c>
       <c r="C79" t="n">
         <v>0.6187670368816109</v>
@@ -1774,7 +1774,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>0.6174671226709815</v>
+        <v>0.6174671226709816</v>
       </c>
       <c r="C80" t="n">
         <v>0.6149326627168407</v>
@@ -1791,10 +1791,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>0.6136145728098651</v>
+        <v>0.613614572809865</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6111338686040091</v>
+        <v>0.611133868604009</v>
       </c>
       <c r="D81" t="n">
         <v>0.9250101337657073</v>
@@ -1808,7 +1808,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>0.6097972019772799</v>
+        <v>0.6097972019772798</v>
       </c>
       <c r="C82" t="n">
         <v>0.6073702871676415</v>
@@ -1845,7 +1845,7 @@
         <v>0.6022665207478259</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5999473000163686</v>
+        <v>0.5999473000163685</v>
       </c>
       <c r="D84" t="n">
         <v>0.9254154843940008</v>
@@ -1893,7 +1893,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>0.5912251763805471</v>
+        <v>0.5912251763805469</v>
       </c>
       <c r="C87" t="n">
         <v>0.5890678291993328</v>
@@ -1910,7 +1910,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>0.5876112039259661</v>
+        <v>0.587611203925966</v>
       </c>
       <c r="C88" t="n">
         <v>0.5855079117907223</v>
@@ -1927,7 +1927,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>0.5840298803113939</v>
+        <v>0.584029880311394</v>
       </c>
       <c r="C89" t="n">
         <v>0.5819806937822015</v>
@@ -1961,7 +1961,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>0.5769637936530326</v>
+        <v>0.5769637936530325</v>
       </c>
       <c r="C91" t="n">
         <v>0.5750229703489942</v>
@@ -2012,7 +2012,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>0.5666009792005687</v>
+        <v>0.5666009792005688</v>
       </c>
       <c r="C94" t="n">
         <v>0.5648230640023398</v>
@@ -2080,10 +2080,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>0.5532112367470818</v>
+        <v>0.5532112367470819</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5516510875353093</v>
+        <v>0.5516510875353094</v>
       </c>
       <c r="D98" t="n">
         <v>0.9256181597081475</v>
@@ -2097,7 +2097,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>0.5499379991431759</v>
+        <v>0.549937999143176</v>
       </c>
       <c r="C99" t="n">
         <v>0.5484323587580882</v>
@@ -2131,7 +2131,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>0.5434784186176945</v>
+        <v>0.5434784186176944</v>
       </c>
       <c r="C101" t="n">
         <v>0.5420818305245507</v>
@@ -2182,7 +2182,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>0.5340018482522075</v>
+        <v>0.5340018482522074</v>
       </c>
       <c r="C104" t="n">
         <v>0.5327688002631282</v>
@@ -2199,10 +2199,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>0.5308985827369747</v>
+        <v>0.5308985827369748</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5297200000434028</v>
+        <v>0.5297200000434029</v>
       </c>
       <c r="D105" t="n">
         <v>0.926023510336441</v>
@@ -2216,7 +2216,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>0.5278226423130001</v>
+        <v>0.5278226423130002</v>
       </c>
       <c r="C106" t="n">
         <v>0.526698483338633</v>
@@ -2236,7 +2236,7 @@
         <v>0.5247737499700792</v>
       </c>
       <c r="C107" t="n">
-        <v>0.5237039617736349</v>
+        <v>0.523703961773635</v>
       </c>
       <c r="D107" t="n">
         <v>0.9261248479935144</v>
@@ -2250,7 +2250,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>0.5217516320636018</v>
+        <v>0.521751632063602</v>
       </c>
       <c r="C108" t="n">
         <v>0.520736149821553</v>
@@ -2267,7 +2267,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>0.5187560181849227</v>
+        <v>0.5187560181849228</v>
       </c>
       <c r="C109" t="n">
         <v>0.5177947647067506</v>
@@ -2284,7 +2284,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>0.5157866410316793</v>
+        <v>0.5157866410316794</v>
       </c>
       <c r="C110" t="n">
         <v>0.5148795263085115</v>
@@ -2301,10 +2301,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>0.5128432362788842</v>
+        <v>0.5128432362788844</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5119901570661791</v>
+        <v>0.5119901570661792</v>
       </c>
       <c r="D111" t="n">
         <v>0.9262261856505878</v>
@@ -2338,7 +2338,7 @@
         <v>0.507033300799385</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5062879280522197</v>
+        <v>0.5062879280522198</v>
       </c>
       <c r="D113" t="n">
         <v>0.9262261856505878</v>
@@ -2355,7 +2355,7 @@
         <v>0.5041662551745111</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5034745251366917</v>
+        <v>0.5034745251366919</v>
       </c>
       <c r="D114" t="n">
         <v>0.9262261856505878</v>
@@ -2369,7 +2369,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>0.501324151912117</v>
+        <v>0.5013241519121171</v>
       </c>
       <c r="C115" t="n">
         <v>0.5006859049176937</v>
@@ -2386,10 +2386,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>0.4985067397151179</v>
+        <v>0.498506739715118</v>
       </c>
       <c r="C116" t="n">
-        <v>0.497921801297989</v>
+        <v>0.4979218012979891</v>
       </c>
       <c r="D116" t="n">
         <v>0.9262261856505878</v>
@@ -2403,10 +2403,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>0.4957137695428654</v>
+        <v>0.4957137695428655</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4951819502286271</v>
+        <v>0.4951819502286272</v>
       </c>
       <c r="D117" t="n">
         <v>0.9262261856505878</v>
@@ -2423,7 +2423,7 @@
         <v>0.4929449945043927</v>
       </c>
       <c r="C118" t="n">
-        <v>0.4924660896366911</v>
+        <v>0.4924660896366912</v>
       </c>
       <c r="D118" t="n">
         <v>0.9262261856505878</v>
@@ -2437,7 +2437,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>0.4902001697564913</v>
+        <v>0.4902001697564914</v>
       </c>
       <c r="C119" t="n">
         <v>0.4897739593575272</v>
@@ -2505,10 +2505,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>0.479455543207509</v>
+        <v>0.4794555432075092</v>
       </c>
       <c r="C123" t="n">
-        <v>0.479237601469541</v>
+        <v>0.4792376014695412</v>
       </c>
       <c r="D123" t="n">
         <v>0.9262261856505878</v>
@@ -2573,7 +2573,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>0.4690750052070796</v>
+        <v>0.4690750052070797</v>
       </c>
       <c r="C127" t="n">
         <v>0.469060572990282</v>
@@ -2593,7 +2593,7 @@
         <v>0.4665350094717643</v>
       </c>
       <c r="C128" t="n">
-        <v>0.466570595721417</v>
+        <v>0.4665705957214171</v>
       </c>
       <c r="D128" t="n">
         <v>0.9266315362788813</v>
@@ -2627,7 +2627,7 @@
         <v>0.4615195783964424</v>
       </c>
       <c r="C130" t="n">
-        <v>0.4616540656875497</v>
+        <v>0.46165406568755</v>
       </c>
       <c r="D130" t="n">
         <v>0.9266315362788813</v>
@@ -2658,7 +2658,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>0.4565887177135329</v>
+        <v>0.456588717713533</v>
       </c>
       <c r="C132" t="n">
         <v>0.456820494319326</v>
@@ -2678,7 +2678,7 @@
         <v>0.4541544396080414</v>
       </c>
       <c r="C133" t="n">
-        <v>0.4544342209651289</v>
+        <v>0.4544342209651291</v>
       </c>
       <c r="D133" t="n">
         <v>0.9266315362788813</v>
@@ -2709,7 +2709,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>0.4493470750761307</v>
+        <v>0.4493470750761309</v>
       </c>
       <c r="C135" t="n">
         <v>0.4497215176560436</v>
@@ -2729,7 +2729,7 @@
         <v>0.4469735470756219</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4473946197277755</v>
+        <v>0.4473946197277757</v>
       </c>
       <c r="D136" t="n">
         <v>0.9267328739359546</v>
@@ -2760,10 +2760,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>0.4422857044446399</v>
+        <v>0.44228570444464</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4427985729021552</v>
+        <v>0.4427985729021553</v>
       </c>
       <c r="D138" t="n">
         <v>0.9268342115930279</v>
@@ -2777,7 +2777,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>0.4399709552530992</v>
+        <v>0.4399709552530993</v>
       </c>
       <c r="C139" t="n">
         <v>0.4405289653229243</v>
@@ -2794,7 +2794,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>0.4376753663886878</v>
+        <v>0.437675366388688</v>
       </c>
       <c r="C140" t="n">
         <v>0.4382779985006932</v>
@@ -2831,7 +2831,7 @@
         <v>0.433140813450099</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4338310874969215</v>
+        <v>0.4338310874969216</v>
       </c>
       <c r="D142" t="n">
         <v>0.9268342115930279</v>
@@ -2862,7 +2862,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0.4286803451655173</v>
+        <v>0.4286803451655174</v>
       </c>
       <c r="C144" t="n">
         <v>0.4294560573083828</v>
@@ -2882,7 +2882,7 @@
         <v>0.426477366634659</v>
       </c>
       <c r="C145" t="n">
-        <v>0.42729494788857</v>
+        <v>0.4272949478885701</v>
       </c>
       <c r="D145" t="n">
         <v>0.9267328739359546</v>
@@ -2896,10 +2896,10 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>0.4242922803392488</v>
+        <v>0.4242922803392489</v>
       </c>
       <c r="C146" t="n">
-        <v>0.4251511525837989</v>
+        <v>0.425151152583799</v>
       </c>
       <c r="D146" t="n">
         <v>0.9267328739359546</v>
@@ -2916,7 +2916,7 @@
         <v>0.4221248791831974</v>
       </c>
       <c r="C147" t="n">
-        <v>0.4230244563465287</v>
+        <v>0.4230244563465289</v>
       </c>
       <c r="D147" t="n">
         <v>0.9267328739359546</v>
@@ -2930,7 +2930,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>0.419974957302778</v>
+        <v>0.4199749573027781</v>
       </c>
       <c r="C148" t="n">
         <v>0.4209146459117165</v>
@@ -2967,7 +2967,7 @@
         <v>0.4157267340847673</v>
       </c>
       <c r="C150" t="n">
-        <v>0.416744838370889</v>
+        <v>0.4167448383708891</v>
       </c>
       <c r="D150" t="n">
         <v>0.9270368869071747</v>
@@ -2981,10 +2981,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0.4136280271834892</v>
+        <v>0.4136280271834893</v>
       </c>
       <c r="C151" t="n">
-        <v>0.4146844237352209</v>
+        <v>0.414684423735221</v>
       </c>
       <c r="D151" t="n">
         <v>0.9270368869071747</v>
@@ -3015,7 +3015,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>0.409480418041488</v>
+        <v>0.4094804180414881</v>
       </c>
       <c r="C153" t="n">
         <v>0.4106115424310525</v>
@@ -3049,10 +3049,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>0.405397889405439</v>
+        <v>0.4053978894054391</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4066012388681734</v>
+        <v>0.4066012388681735</v>
       </c>
       <c r="D155" t="n">
         <v>0.9270368869071747</v>
@@ -3069,7 +3069,7 @@
         <v>0.403380537489278</v>
       </c>
       <c r="C156" t="n">
-        <v>0.4046190529957402</v>
+        <v>0.4046190529957403</v>
       </c>
       <c r="D156" t="n">
         <v>0.9270368869071747</v>
@@ -3083,10 +3083,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>0.4013788665877502</v>
+        <v>0.4013788665877503</v>
       </c>
       <c r="C157" t="n">
-        <v>0.4026519140945837</v>
+        <v>0.4026519140945838</v>
       </c>
       <c r="D157" t="n">
         <v>0.9270368869071747</v>
@@ -3103,7 +3103,7 @@
         <v>0.3993926825876689</v>
       </c>
       <c r="C158" t="n">
-        <v>0.4006996265117829</v>
+        <v>0.400699626511783</v>
       </c>
       <c r="D158" t="n">
         <v>0.9270368869071747</v>
@@ -3171,7 +3171,7 @@
         <v>0.3915989672715754</v>
       </c>
       <c r="C162" t="n">
-        <v>0.3930351309793384</v>
+        <v>0.3930351309793385</v>
       </c>
       <c r="D162" t="n">
         <v>0.9268342115930279</v>
@@ -3185,7 +3185,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>0.3896873391582835</v>
+        <v>0.3896873391582836</v>
       </c>
       <c r="C163" t="n">
         <v>0.3911542189525181</v>
@@ -3202,10 +3202,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>0.3877900522114356</v>
+        <v>0.3877900522114358</v>
       </c>
       <c r="C164" t="n">
-        <v>0.3892870156123827</v>
+        <v>0.3892870156123828</v>
       </c>
       <c r="D164" t="n">
         <v>0.9268342115930279</v>
@@ -3253,7 +3253,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>0.3821823564067677</v>
+        <v>0.3821823564067678</v>
       </c>
       <c r="C167" t="n">
         <v>0.3837658037556024</v>
@@ -3270,7 +3270,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>0.380340554374946</v>
+        <v>0.3803405543749461</v>
       </c>
       <c r="C168" t="n">
         <v>0.3819515861688499</v>
@@ -3287,7 +3287,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>0.3785121555607923</v>
+        <v>0.3785121555607924</v>
       </c>
       <c r="C169" t="n">
         <v>0.3801501574285223</v>
@@ -3304,10 +3304,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>0.376696973255493</v>
+        <v>0.3766969732554931</v>
       </c>
       <c r="C170" t="n">
-        <v>0.378361336067163</v>
+        <v>0.3783613360671631</v>
       </c>
       <c r="D170" t="n">
         <v>0.9266315362788813</v>
@@ -3358,7 +3358,7 @@
         <v>0.3713288599219611</v>
       </c>
       <c r="C173" t="n">
-        <v>0.3730687111877458</v>
+        <v>0.3730687111877459</v>
       </c>
       <c r="D173" t="n">
         <v>0.9270368869071747</v>
@@ -3372,7 +3372,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0.3695646784428112</v>
+        <v>0.3695646784428113</v>
       </c>
       <c r="C174" t="n">
         <v>0.371328517219879</v>
@@ -3389,7 +3389,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>0.3678127810885789</v>
+        <v>0.367812781088579</v>
       </c>
       <c r="C175" t="n">
         <v>0.3696000325054224</v>
@@ -3406,7 +3406,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>0.366072981552705</v>
+        <v>0.3660729815527051</v>
       </c>
       <c r="C176" t="n">
         <v>0.3678830792619724</v>
@@ -3426,7 +3426,7 @@
         <v>0.3643450937045877</v>
       </c>
       <c r="C177" t="n">
-        <v>0.3661774804854989</v>
+        <v>0.366177480485499</v>
       </c>
       <c r="D177" t="n">
         <v>0.9273408998783949</v>
@@ -3443,7 +3443,7 @@
         <v>0.3626289317249183</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3644830601184175</v>
+        <v>0.3644830601184176</v>
       </c>
       <c r="D178" t="n">
         <v>0.9274422375354682</v>
@@ -3457,7 +3457,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>0.3609243102976983</v>
+        <v>0.3609243102976984</v>
       </c>
       <c r="C179" t="n">
         <v>0.3627996432827054</v>
@@ -3525,10 +3525,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>0.3542175580918455</v>
+        <v>0.3542175580918456</v>
       </c>
       <c r="C183" t="n">
-        <v>0.3561725747639853</v>
+        <v>0.3561725747639854</v>
       </c>
       <c r="D183" t="n">
         <v>0.9275435751925416</v>
@@ -3545,7 +3545,7 @@
         <v>0.3525678999594746</v>
       </c>
       <c r="C184" t="n">
-        <v>0.3545416204558144</v>
+        <v>0.3545416204558145</v>
       </c>
       <c r="D184" t="n">
         <v>0.9275435751925416</v>
@@ -3596,7 +3596,7 @@
         <v>0.3476810108074096</v>
       </c>
       <c r="C187" t="n">
-        <v>0.3497081729729238</v>
+        <v>0.3497081729729239</v>
       </c>
       <c r="D187" t="n">
         <v>0.9275435751925416</v>
@@ -3729,7 +3729,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>0.3350784319890839</v>
+        <v>0.335078431989084</v>
       </c>
       <c r="C195" t="n">
         <v>0.3372323143255243</v>
@@ -3800,7 +3800,7 @@
         <v>0.328999362991223</v>
       </c>
       <c r="C199" t="n">
-        <v>0.3312114772950666</v>
+        <v>0.3312114772950667</v>
       </c>
       <c r="D199" t="n">
         <v>0.9269355492501014</v>
@@ -3814,7 +3814,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>0.3275024976370859</v>
+        <v>0.3275024976370861</v>
       </c>
       <c r="C200" t="n">
         <v>0.3297290355750326</v>
@@ -3899,7 +3899,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>0.3201604205752699</v>
+        <v>0.32016042057527</v>
       </c>
       <c r="C205" t="n">
         <v>0.3224603852819516</v>
@@ -3936,7 +3936,7 @@
         <v>0.3172934294451378</v>
       </c>
       <c r="C207" t="n">
-        <v>0.3196241238717697</v>
+        <v>0.3196241238717699</v>
       </c>
       <c r="D207" t="n">
         <v>0.9274422375354682</v>
@@ -3953,7 +3953,7 @@
         <v>0.3158758758586084</v>
       </c>
       <c r="C208" t="n">
-        <v>0.3182223635407098</v>
+        <v>0.3182223635407099</v>
       </c>
       <c r="D208" t="n">
         <v>0.9273408998783949</v>
@@ -3987,7 +3987,7 @@
         <v>0.3130741136915515</v>
       </c>
       <c r="C210" t="n">
-        <v>0.315453164852131</v>
+        <v>0.3154531648521311</v>
       </c>
       <c r="D210" t="n">
         <v>0.9275435751925416</v>
@@ -4001,10 +4001,10 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>0.3116905171591145</v>
+        <v>0.3116905171591146</v>
       </c>
       <c r="C211" t="n">
-        <v>0.3140863708113404</v>
+        <v>0.3140863708113405</v>
       </c>
       <c r="D211" t="n">
         <v>0.9275435751925416</v>
@@ -4052,10 +4052,10 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>0.3076125172421127</v>
+        <v>0.3076125172421128</v>
       </c>
       <c r="C214" t="n">
-        <v>0.310060937504971</v>
+        <v>0.3100609375049711</v>
       </c>
       <c r="D214" t="n">
         <v>0.9284556141062018</v>
@@ -4086,10 +4086,10 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>0.3049573227267444</v>
+        <v>0.3049573227267445</v>
       </c>
       <c r="C216" t="n">
-        <v>0.3074425437225026</v>
+        <v>0.3074425437225027</v>
       </c>
       <c r="D216" t="n">
         <v>0.9284556141062018</v>
@@ -4106,7 +4106,7 @@
         <v>0.303649500540187</v>
       </c>
       <c r="C217" t="n">
-        <v>0.3061536120817329</v>
+        <v>0.306153612081733</v>
       </c>
       <c r="D217" t="n">
         <v>0.9282529387920552</v>
@@ -4120,10 +4120,10 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>0.3023551218774118</v>
+        <v>0.3023551218774119</v>
       </c>
       <c r="C218" t="n">
-        <v>0.3048784262599048</v>
+        <v>0.3048784262599049</v>
       </c>
       <c r="D218" t="n">
         <v>0.9280502634779084</v>
@@ -4140,7 +4140,7 @@
         <v>0.301074339986167</v>
       </c>
       <c r="C219" t="n">
-        <v>0.3036171182736992</v>
+        <v>0.3036171182736994</v>
       </c>
       <c r="D219" t="n">
         <v>0.927948925820835</v>
@@ -4205,10 +4205,10 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>0.2960889766267985</v>
+        <v>0.2960889766267986</v>
       </c>
       <c r="C223" t="n">
-        <v>0.2987120042253329</v>
+        <v>0.298712004225333</v>
       </c>
       <c r="D223" t="n">
         <v>0.9290636400486421</v>
@@ -4256,10 +4256,10 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>0.2924948577000996</v>
+        <v>0.2924948577000997</v>
       </c>
       <c r="C226" t="n">
-        <v>0.2951799249534023</v>
+        <v>0.2951799249534025</v>
       </c>
       <c r="D226" t="n">
         <v>0.9291649777057155</v>
@@ -4276,7 +4276,7 @@
         <v>0.2913240693451696</v>
       </c>
       <c r="C227" t="n">
-        <v>0.2940300663620999</v>
+        <v>0.2940300663621</v>
       </c>
       <c r="D227" t="n">
         <v>0.9295703283340089</v>
@@ -4327,7 +4327,7 @@
         <v>0.2878914897959569</v>
       </c>
       <c r="C230" t="n">
-        <v>0.2906608241888409</v>
+        <v>0.290660824188841</v>
       </c>
       <c r="D230" t="n">
         <v>0.9297730036481556</v>
@@ -4341,7 +4341,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>0.286773287749139</v>
+        <v>0.2867732877491389</v>
       </c>
       <c r="C231" t="n">
         <v>0.2895638818654298</v>
@@ -4395,7 +4395,7 @@
         <v>0.2834937303700546</v>
       </c>
       <c r="C234" t="n">
-        <v>0.2863484427878632</v>
+        <v>0.2863484427878633</v>
       </c>
       <c r="D234" t="n">
         <v>0.9290636400486421</v>
@@ -4426,7 +4426,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>0.2813676164395016</v>
+        <v>0.2813676164395017</v>
       </c>
       <c r="C236" t="n">
         <v>0.2842653133254698</v>
@@ -4443,7 +4443,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>0.2803219299308028</v>
+        <v>0.2803219299308029</v>
       </c>
       <c r="C237" t="n">
         <v>0.2832411826992211</v>
@@ -4460,7 +4460,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>0.2792875065121684</v>
+        <v>0.2792875065121685</v>
       </c>
       <c r="C238" t="n">
         <v>0.2822283556622023</v>
@@ -4494,7 +4494,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>0.2772515046953155</v>
+        <v>0.2772515046953156</v>
       </c>
       <c r="C240" t="n">
         <v>0.2802356649692442</v>
@@ -4511,10 +4511,10 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>0.2762494609908558</v>
+        <v>0.2762494609908559</v>
       </c>
       <c r="C241" t="n">
-        <v>0.2792553351397411</v>
+        <v>0.2792553351397412</v>
       </c>
       <c r="D241" t="n">
         <v>0.9294689906769356</v>
@@ -4531,7 +4531,7 @@
         <v>0.2752577514155909</v>
       </c>
       <c r="C242" t="n">
-        <v>0.2782853780140945</v>
+        <v>0.2782853780140946</v>
       </c>
       <c r="D242" t="n">
         <v>0.9297730036481556</v>
@@ -4548,7 +4548,7 @@
         <v>0.274276153573922</v>
       </c>
       <c r="C243" t="n">
-        <v>0.2773255710638803</v>
+        <v>0.2773255710638804</v>
       </c>
       <c r="D243" t="n">
         <v>0.9296716659910823</v>
@@ -4616,7 +4616,7 @@
         <v>0.2704466153703774</v>
       </c>
       <c r="C247" t="n">
-        <v>0.2735835773472536</v>
+        <v>0.2735835773472537</v>
       </c>
       <c r="D247" t="n">
         <v>0.9308877178759627</v>
@@ -4630,7 +4630,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>0.2695124274853295</v>
+        <v>0.2695124274853296</v>
       </c>
       <c r="C248" t="n">
         <v>0.2726713692284305</v>
@@ -4647,7 +4647,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>0.2685871320902842</v>
+        <v>0.2685871320902843</v>
       </c>
       <c r="C249" t="n">
         <v>0.271768090013478</v>
@@ -4732,7 +4732,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>0.2640878475197191</v>
+        <v>0.2640878475197192</v>
       </c>
       <c r="C254" t="n">
         <v>0.267379401073232</v>
@@ -4752,7 +4752,7 @@
         <v>0.2632122691815653</v>
       </c>
       <c r="C255" t="n">
-        <v>0.2665260366189228</v>
+        <v>0.2665260366189229</v>
       </c>
       <c r="D255" t="n">
         <v>0.9308877178759627</v>
@@ -4987,7 +4987,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>0.2517061798988502</v>
+        <v>0.2517061798988503</v>
       </c>
       <c r="C269" t="n">
         <v>0.2553330741550467</v>
@@ -5075,7 +5075,7 @@
         <v>0.2479009427681762</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2516399915727056</v>
+        <v>0.2516399915727057</v>
       </c>
       <c r="D274" t="n">
         <v>0.935346574787191</v>
@@ -5140,7 +5140,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>0.2449589070649326</v>
+        <v>0.2449589070649325</v>
       </c>
       <c r="C278" t="n">
         <v>0.2487875116219467</v>
@@ -5208,7 +5208,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>0.2421022864334341</v>
+        <v>0.2421022864334342</v>
       </c>
       <c r="C282" t="n">
         <v>0.2460201559925728</v>
@@ -5225,7 +5225,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>0.2414009463159819</v>
+        <v>0.241400946315982</v>
       </c>
       <c r="C283" t="n">
         <v>0.245341071942243</v>
@@ -5262,7 +5262,7 @@
         <v>0.2400131817831443</v>
       </c>
       <c r="C285" t="n">
-        <v>0.2439977340027782</v>
+        <v>0.2439977340027783</v>
       </c>
       <c r="D285" t="n">
         <v>0.9370693149574382</v>
@@ -5276,7 +5276,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>0.23932663155609</v>
+        <v>0.2393266315560901</v>
       </c>
       <c r="C286" t="n">
         <v>0.2433333505917022</v>
@@ -5364,7 +5364,7 @@
         <v>0.2359648125359251</v>
       </c>
       <c r="C291" t="n">
-        <v>0.2400818287834761</v>
+        <v>0.2400818287834762</v>
       </c>
       <c r="D291" t="n">
         <v>0.9379813538710985</v>
@@ -5466,7 +5466,7 @@
         <v>0.2320793867600794</v>
       </c>
       <c r="C297" t="n">
-        <v>0.2363273514948819</v>
+        <v>0.236327351494882</v>
       </c>
       <c r="D297" t="n">
         <v>0.9395014187271991</v>
@@ -5480,7 +5480,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.2314468713449596</v>
+        <v>0.2314468713449597</v>
       </c>
       <c r="C298" t="n">
         <v>0.2357164884191131</v>
@@ -5531,7 +5531,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>0.2295741797804814</v>
+        <v>0.2295741797804815</v>
       </c>
       <c r="C301" t="n">
         <v>0.2339084270045309</v>
@@ -5565,10 +5565,10 @@
         <v>302</v>
       </c>
       <c r="B303" t="n">
-        <v>0.2283459805839178</v>
+        <v>0.2283459805839179</v>
       </c>
       <c r="C303" t="n">
-        <v>0.2327230271589599</v>
+        <v>0.23272302715896</v>
       </c>
       <c r="D303" t="n">
         <v>0.9397040940413458</v>
@@ -5602,7 +5602,7 @@
         <v>0.2271335857829223</v>
       </c>
       <c r="C305" t="n">
-        <v>0.2315531881371336</v>
+        <v>0.2315531881371337</v>
       </c>
       <c r="D305" t="n">
         <v>0.9397040940413458</v>
@@ -5619,7 +5619,7 @@
         <v>0.2265332103826425</v>
       </c>
       <c r="C306" t="n">
-        <v>0.2309739957358802</v>
+        <v>0.2309739957358803</v>
       </c>
       <c r="D306" t="n">
         <v>0.9398054316984191</v>
@@ -5636,7 +5636,7 @@
         <v>0.2259366619576722</v>
       </c>
       <c r="C307" t="n">
-        <v>0.2303985651964192</v>
+        <v>0.2303985651964193</v>
       </c>
       <c r="D307" t="n">
         <v>0.9398054316984191</v>
@@ -5650,10 +5650,10 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>0.2253439006083791</v>
+        <v>0.2253439006083792</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2298268552547719</v>
+        <v>0.229826855254772</v>
       </c>
       <c r="D308" t="n">
         <v>0.9398054316984191</v>
@@ -5667,7 +5667,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>0.2247548871045446</v>
+        <v>0.2247548871045447</v>
       </c>
       <c r="C309" t="n">
         <v>0.2292588253368361</v>
@@ -5718,10 +5718,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>0.2230099509821174</v>
+        <v>0.2230099509821175</v>
       </c>
       <c r="C312" t="n">
-        <v>0.2275764199114285</v>
+        <v>0.2275764199114286</v>
       </c>
       <c r="D312" t="n">
         <v>0.9400081070125659</v>
@@ -5738,7 +5738,7 @@
         <v>0.2224355492496871</v>
       </c>
       <c r="C313" t="n">
-        <v>0.227022717451362</v>
+        <v>0.2270227174513621</v>
       </c>
       <c r="D313" t="n">
         <v>0.9398054316984191</v>
@@ -5752,7 +5752,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>0.2218647085680598</v>
+        <v>0.2218647085680599</v>
       </c>
       <c r="C314" t="n">
         <v>0.2264725018112023</v>
@@ -5874,7 +5874,7 @@
         <v>0.2179656083805469</v>
       </c>
       <c r="C321" t="n">
-        <v>0.2227155987890663</v>
+        <v>0.2227155987890664</v>
       </c>
       <c r="D321" t="n">
         <v>0.9416295095257398</v>
@@ -5888,7 +5888,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>0.2174220178898236</v>
+        <v>0.2174220178898237</v>
       </c>
       <c r="C322" t="n">
         <v>0.2221919974383185</v>
@@ -5959,7 +5959,7 @@
         <v>0.2152799352140236</v>
       </c>
       <c r="C326" t="n">
-        <v>0.2201290171322182</v>
+        <v>0.2201290171322183</v>
       </c>
       <c r="D326" t="n">
         <v>0.9419335224969598</v>
@@ -6007,7 +6007,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>0.2137064161769597</v>
+        <v>0.2137064161769598</v>
       </c>
       <c r="C329" t="n">
         <v>0.218613900779021</v>
@@ -6109,10 +6109,10 @@
         <v>334</v>
       </c>
       <c r="B335" t="n">
-        <v>0.2106409552040522</v>
+        <v>0.2106409552040523</v>
       </c>
       <c r="C335" t="n">
-        <v>0.2156627652060927</v>
+        <v>0.2156627652060928</v>
       </c>
       <c r="D335" t="n">
         <v>0.9421361978111066</v>
@@ -6126,7 +6126,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="n">
-        <v>0.2101402969549571</v>
+        <v>0.2101402969549572</v>
       </c>
       <c r="C336" t="n">
         <v>0.2151808303802623</v>
@@ -6211,7 +6211,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>0.2076793594842723</v>
+        <v>0.2076793594842724</v>
       </c>
       <c r="C341" t="n">
         <v>0.2128120499613373</v>
@@ -6282,7 +6282,7 @@
         <v>0.2057599282747435</v>
       </c>
       <c r="C345" t="n">
-        <v>0.2109645561507204</v>
+        <v>0.2109645561507205</v>
       </c>
       <c r="D345" t="n">
         <v>0.9436562626672071</v>
@@ -6486,7 +6486,7 @@
         <v>0.200248888563046</v>
       </c>
       <c r="C357" t="n">
-        <v>0.2056594804996645</v>
+        <v>0.2056594804996646</v>
       </c>
       <c r="D357" t="n">
         <v>0.9458856911228213</v>
@@ -6690,7 +6690,7 @@
         <v>0.1950801168545928</v>
       </c>
       <c r="C369" t="n">
-        <v>0.2006815504126995</v>
+        <v>0.2006815504126994</v>
       </c>
       <c r="D369" t="n">
         <v>0.946088366436968</v>
@@ -6724,7 +6724,7 @@
         <v>0.1942495672604584</v>
       </c>
       <c r="C371" t="n">
-        <v>0.1998813265574494</v>
+        <v>0.1998813265574495</v>
       </c>
       <c r="D371" t="n">
         <v>0.9463923794081881</v>
@@ -6843,7 +6843,7 @@
         <v>0.1914082984896933</v>
       </c>
       <c r="C378" t="n">
-        <v>0.1971428817769572</v>
+        <v>0.1971428817769573</v>
       </c>
       <c r="D378" t="n">
         <v>0.947203080664775</v>
@@ -6874,10 +6874,10 @@
         <v>379</v>
       </c>
       <c r="B380" t="n">
-        <v>0.190614720371524</v>
+        <v>0.1906147203715239</v>
       </c>
       <c r="C380" t="n">
-        <v>0.1963777402216956</v>
+        <v>0.1963777402216957</v>
       </c>
       <c r="D380" t="n">
         <v>0.947203080664775</v>
@@ -6945,7 +6945,7 @@
         <v>0.1890510246080092</v>
       </c>
       <c r="C384" t="n">
-        <v>0.1948696738581531</v>
+        <v>0.1948696738581532</v>
       </c>
       <c r="D384" t="n">
         <v>0.9479124442642886</v>
@@ -7013,7 +7013,7 @@
         <v>0.1875178048940322</v>
       </c>
       <c r="C388" t="n">
-        <v>0.1933904403801039</v>
+        <v>0.193390440380104</v>
       </c>
       <c r="D388" t="n">
         <v>0.9479124442642886</v>
@@ -7044,7 +7044,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="n">
-        <v>0.1867623319001363</v>
+        <v>0.1867623319001364</v>
       </c>
       <c r="C390" t="n">
         <v>0.1926613506667284</v>
@@ -7078,7 +7078,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="n">
-        <v>0.1860141330983846</v>
+        <v>0.1860141330983847</v>
       </c>
       <c r="C392" t="n">
         <v>0.1919391322928113</v>
@@ -7095,7 +7095,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="n">
-        <v>0.1856427271497507</v>
+        <v>0.1856427271497508</v>
       </c>
       <c r="C393" t="n">
         <v>0.1915805664067744</v>
@@ -7132,7 +7132,7 @@
         <v>0.1849052347394892</v>
       </c>
       <c r="C395" t="n">
-        <v>0.1908684557257478</v>
+        <v>0.1908684557257479</v>
       </c>
       <c r="D395" t="n">
         <v>0.9483177948925821</v>
@@ -7200,7 +7200,7 @@
         <v>0.1834511595612705</v>
       </c>
       <c r="C399" t="n">
-        <v>0.189463961548144</v>
+        <v>0.1894639615481439</v>
       </c>
       <c r="D399" t="n">
         <v>0.9488244831779489</v>
@@ -7316,7 +7316,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>0.1809715004268588</v>
+        <v>0.1809715004268587</v>
       </c>
       <c r="C406" t="n">
         <v>0.1870673452139339</v>
@@ -7350,7 +7350,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="n">
-        <v>0.1802777404562394</v>
+        <v>0.1802777404562393</v>
       </c>
       <c r="C408" t="n">
         <v>0.186396458245494</v>
@@ -7588,7 +7588,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>0.1755948005527572</v>
+        <v>0.1755948005527573</v>
       </c>
       <c r="C422" t="n">
         <v>0.1818634011055075</v>
@@ -7622,7 +7622,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="n">
-        <v>0.174949557905794</v>
+        <v>0.1749495579057939</v>
       </c>
       <c r="C424" t="n">
         <v>0.1812381541389627</v>
@@ -7707,7 +7707,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="n">
-        <v>0.1733611980361246</v>
+        <v>0.1733611980361247</v>
       </c>
       <c r="C429" t="n">
         <v>0.1796982924929868</v>
@@ -7727,7 +7727,7 @@
         <v>0.173047692363922</v>
       </c>
       <c r="C430" t="n">
-        <v>0.1793942346509321</v>
+        <v>0.179394234650932</v>
       </c>
       <c r="D430" t="n">
         <v>0.9505472233481962</v>
@@ -7877,10 +7877,10 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>0.170286581939733</v>
+        <v>0.1702865819397331</v>
       </c>
       <c r="C439" t="n">
-        <v>0.1767144831930468</v>
+        <v>0.1767144831930469</v>
       </c>
       <c r="D439" t="n">
         <v>0.9511552492906364</v>
@@ -7894,7 +7894,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="n">
-        <v>0.1699863462243247</v>
+        <v>0.1699863462243248</v>
       </c>
       <c r="C440" t="n">
         <v>0.1764228879643568</v>
@@ -7982,7 +7982,7 @@
         <v>0.1685041940468851</v>
       </c>
       <c r="C445" t="n">
-        <v>0.1749827746530861</v>
+        <v>0.174982774653086</v>
       </c>
       <c r="D445" t="n">
         <v>0.9514592622618565</v>
@@ -8067,7 +8067,7 @@
         <v>0.1670530077566878</v>
       </c>
       <c r="C450" t="n">
-        <v>0.1735717297023135</v>
+        <v>0.1735717297023134</v>
       </c>
       <c r="D450" t="n">
         <v>0.9519659505472233</v>
@@ -8489,7 +8489,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="n">
-        <v>0.1602285155596228</v>
+        <v>0.1602285155596227</v>
       </c>
       <c r="C475" t="n">
         <v>0.1669214209370062</v>
@@ -8574,7 +8574,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="n">
-        <v>0.158943786604481</v>
+        <v>0.1589437866044811</v>
       </c>
       <c r="C480" t="n">
         <v>0.1656665999284982</v>
@@ -8591,7 +8591,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="n">
-        <v>0.1586898447180909</v>
+        <v>0.158689844718091</v>
       </c>
       <c r="C481" t="n">
         <v>0.1654184554081967</v>
@@ -8798,7 +8798,7 @@
         <v>0.1557177997022716</v>
       </c>
       <c r="C493" t="n">
-        <v>0.1625113765132868</v>
+        <v>0.1625113765132867</v>
       </c>
       <c r="D493" t="n">
         <v>0.9550060802594244</v>
@@ -8849,7 +8849,7 @@
         <v>0.1549957924013959</v>
       </c>
       <c r="C496" t="n">
-        <v>0.1618043301681973</v>
+        <v>0.1618043301681974</v>
       </c>
       <c r="D496" t="n">
         <v>0.9556141062018646</v>
@@ -8914,7 +8914,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="n">
-        <v>0.1540456802684347</v>
+        <v>0.1540456802684346</v>
       </c>
       <c r="C500" t="n">
         <v>0.1608734030720875</v>
@@ -9220,10 +9220,10 @@
         <v>517</v>
       </c>
       <c r="B518" t="n">
-        <v>0.1499389826844648</v>
+        <v>0.1499389826844647</v>
       </c>
       <c r="C518" t="n">
-        <v>0.1568428460761296</v>
+        <v>0.1568428460761295</v>
       </c>
       <c r="D518" t="n">
         <v>0.9562221321443048</v>
@@ -9308,7 +9308,7 @@
         <v>0.1488445864318859</v>
       </c>
       <c r="C523" t="n">
-        <v>0.1557668177302848</v>
+        <v>0.1557668177302849</v>
       </c>
       <c r="D523" t="n">
         <v>0.9561207944872314</v>
@@ -9441,7 +9441,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="n">
-        <v>0.1471328340816925</v>
+        <v>0.1471328340816924</v>
       </c>
       <c r="C531" t="n">
         <v>0.1540821087748456</v>
@@ -9458,10 +9458,10 @@
         <v>531</v>
       </c>
       <c r="B532" t="n">
-        <v>0.1469221658363613</v>
+        <v>0.1469221658363612</v>
       </c>
       <c r="C532" t="n">
-        <v>0.1538746241447597</v>
+        <v>0.1538746241447596</v>
       </c>
       <c r="D532" t="n">
         <v>0.9559181191730847</v>
@@ -9699,7 +9699,7 @@
         <v>0.1440461922469652</v>
       </c>
       <c r="C546" t="n">
-        <v>0.1510388448706491</v>
+        <v>0.151038844870649</v>
       </c>
       <c r="D546" t="n">
         <v>0.9569314957438184</v>
@@ -9798,10 +9798,10 @@
         <v>551</v>
       </c>
       <c r="B552" t="n">
-        <v>0.142853741004954</v>
+        <v>0.1428537410049539</v>
       </c>
       <c r="C552" t="n">
-        <v>0.1498612205022806</v>
+        <v>0.1498612205022805</v>
       </c>
       <c r="D552" t="n">
         <v>0.9571341710579652</v>
@@ -9968,7 +9968,7 @@
         <v>561</v>
       </c>
       <c r="B562" t="n">
-        <v>0.1409164722851405</v>
+        <v>0.1409164722851406</v>
       </c>
       <c r="C562" t="n">
         <v>0.1479456339582896</v>
@@ -10056,7 +10056,7 @@
         <v>0.1399703059663698</v>
       </c>
       <c r="C567" t="n">
-        <v>0.1470089356003898</v>
+        <v>0.1470089356003897</v>
       </c>
       <c r="D567" t="n">
         <v>0.957640859343332</v>
@@ -10107,7 +10107,7 @@
         <v>0.1394095203976105</v>
       </c>
       <c r="C570" t="n">
-        <v>0.1464534025988696</v>
+        <v>0.1464534025988695</v>
       </c>
       <c r="D570" t="n">
         <v>0.9577421970004053</v>
@@ -10192,7 +10192,7 @@
         <v>0.1384860808105733</v>
       </c>
       <c r="C575" t="n">
-        <v>0.145538015198908</v>
+        <v>0.1455380151989081</v>
       </c>
       <c r="D575" t="n">
         <v>0.9577421970004053</v>
@@ -10240,7 +10240,7 @@
         <v>577</v>
       </c>
       <c r="B578" t="n">
-        <v>0.1379385799298402</v>
+        <v>0.1379385799298403</v>
       </c>
       <c r="C578" t="n">
         <v>0.144994929612239</v>
@@ -10274,7 +10274,7 @@
         <v>579</v>
       </c>
       <c r="B580" t="n">
-        <v>0.1375762548503598</v>
+        <v>0.1375762548503599</v>
       </c>
       <c r="C580" t="n">
         <v>0.1446353765102489</v>
@@ -10311,7 +10311,7 @@
         <v>0.1372160377358594</v>
       </c>
       <c r="C582" t="n">
-        <v>0.1442777950353452</v>
+        <v>0.1442777950353451</v>
       </c>
       <c r="D582" t="n">
         <v>0.9577421970004053</v>
@@ -10651,7 +10651,7 @@
         <v>0.1337239463973151</v>
       </c>
       <c r="C602" t="n">
-        <v>0.1408046928945866</v>
+        <v>0.1408046928945867</v>
       </c>
       <c r="D602" t="n">
         <v>0.9585528982569923</v>
@@ -10750,7 +10750,7 @@
         <v>607</v>
       </c>
       <c r="B608" t="n">
-        <v>0.1327130434945982</v>
+        <v>0.1327130434945983</v>
       </c>
       <c r="C608" t="n">
         <v>0.1397969126950045</v>
@@ -10903,7 +10903,7 @@
         <v>616</v>
       </c>
       <c r="B617" t="n">
-        <v>0.1312261379816665</v>
+        <v>0.1312261379816666</v>
       </c>
       <c r="C617" t="n">
         <v>0.1383124857425128</v>
@@ -10974,7 +10974,7 @@
         <v>0.1305761822613148</v>
       </c>
       <c r="C621" t="n">
-        <v>0.1376627832798423</v>
+        <v>0.1376627832798422</v>
       </c>
       <c r="D621" t="n">
         <v>0.9589582488852858</v>
@@ -11042,7 +11042,7 @@
         <v>0.1299326915072939</v>
       </c>
       <c r="C625" t="n">
-        <v>0.1370190235918173</v>
+        <v>0.1370190235918174</v>
       </c>
       <c r="D625" t="n">
         <v>0.9593635995135793</v>
@@ -11076,7 +11076,7 @@
         <v>0.1296133202744687</v>
       </c>
       <c r="C627" t="n">
-        <v>0.1366993219272104</v>
+        <v>0.1366993219272103</v>
       </c>
       <c r="D627" t="n">
         <v>0.9593635995135793</v>
@@ -11416,7 +11416,7 @@
         <v>0.1265021934117741</v>
       </c>
       <c r="C647" t="n">
-        <v>0.1335776844776476</v>
+        <v>0.1335776844776477</v>
       </c>
       <c r="D647" t="n">
         <v>0.9595662748277259</v>
@@ -11498,7 +11498,7 @@
         <v>651</v>
       </c>
       <c r="B652" t="n">
-        <v>0.1257466535372237</v>
+        <v>0.1257466535372236</v>
       </c>
       <c r="C652" t="n">
         <v>0.1328174641438943</v>
@@ -11637,7 +11637,7 @@
         <v>0.1245551659590271</v>
       </c>
       <c r="C660" t="n">
-        <v>0.131616778729678</v>
+        <v>0.1316167787296779</v>
       </c>
       <c r="D660" t="n">
         <v>0.9601743007701662</v>
@@ -11668,7 +11668,7 @@
         <v>661</v>
       </c>
       <c r="B662" t="n">
-        <v>0.1242605466026741</v>
+        <v>0.1242605466026742</v>
       </c>
       <c r="C662" t="n">
         <v>0.1313195318671355</v>
@@ -11957,7 +11957,7 @@
         <v>678</v>
       </c>
       <c r="B679" t="n">
-        <v>0.1218064718841086</v>
+        <v>0.1218064718841087</v>
       </c>
       <c r="C679" t="n">
         <v>0.1288378757117073</v>
@@ -12076,7 +12076,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>0.120821033275102</v>
+        <v>0.1208210332751019</v>
       </c>
       <c r="C686" t="n">
         <v>0.1278383978973607</v>
@@ -12334,7 +12334,7 @@
         <v>0.1187559768355313</v>
       </c>
       <c r="C701" t="n">
-        <v>0.1257382264982989</v>
+        <v>0.1257382264982988</v>
       </c>
       <c r="D701" t="n">
         <v>0.9611876773408998</v>
@@ -12402,7 +12402,7 @@
         <v>0.1182156893750938</v>
       </c>
       <c r="C705" t="n">
-        <v>0.1251874710346663</v>
+        <v>0.1251874710346662</v>
       </c>
       <c r="D705" t="n">
         <v>0.9608836643696798</v>
@@ -12674,7 +12674,7 @@
         <v>0.1160967319144715</v>
       </c>
       <c r="C721" t="n">
-        <v>0.1230224125113588</v>
+        <v>0.1230224125113587</v>
       </c>
       <c r="D721" t="n">
         <v>0.9616943656262668</v>
@@ -12858,7 +12858,7 @@
         <v>731</v>
       </c>
       <c r="B732" t="n">
-        <v>0.1146780911618537</v>
+        <v>0.1146780911618536</v>
       </c>
       <c r="C732" t="n">
         <v>0.1215685938831973</v>
@@ -12909,7 +12909,7 @@
         <v>734</v>
       </c>
       <c r="B735" t="n">
-        <v>0.1142964685234771</v>
+        <v>0.1142964685234772</v>
       </c>
       <c r="C735" t="n">
         <v>0.121176953916371</v>
@@ -13184,7 +13184,7 @@
         <v>0.1122987365221485</v>
       </c>
       <c r="C751" t="n">
-        <v>0.1191232994066745</v>
+        <v>0.1191232994066744</v>
       </c>
       <c r="D751" t="n">
         <v>0.9624037292257803</v>
@@ -13303,7 +13303,7 @@
         <v>0.1114444086678757</v>
       </c>
       <c r="C758" t="n">
-        <v>0.1182434577301288</v>
+        <v>0.1182434577301287</v>
       </c>
       <c r="D758" t="n">
         <v>0.9624037292257803</v>
@@ -13337,7 +13337,7 @@
         <v>0.1112024945154159</v>
       </c>
       <c r="C760" t="n">
-        <v>0.1179941666995515</v>
+        <v>0.1179941666995514</v>
       </c>
       <c r="D760" t="n">
         <v>0.9624037292257803</v>
@@ -13436,7 +13436,7 @@
         <v>765</v>
       </c>
       <c r="B766" t="n">
-        <v>0.1104825357878946</v>
+        <v>0.1104825357878945</v>
       </c>
       <c r="C766" t="n">
         <v>0.1172518921643379</v>
@@ -13640,7 +13640,7 @@
         <v>777</v>
       </c>
       <c r="B778" t="n">
-        <v>0.109068488644241</v>
+        <v>0.1090684886442409</v>
       </c>
       <c r="C778" t="n">
         <v>0.1157926543573217</v>
@@ -14116,7 +14116,7 @@
         <v>805</v>
       </c>
       <c r="B806" t="n">
-        <v>0.1059013177167929</v>
+        <v>0.105901317716793</v>
       </c>
       <c r="C806" t="n">
         <v>0.1125200261433523</v>
@@ -14136,7 +14136,7 @@
         <v>0.1057915812459502</v>
       </c>
       <c r="C807" t="n">
-        <v>0.1124065785131534</v>
+        <v>0.1124065785131533</v>
       </c>
       <c r="D807" t="n">
         <v>0.9636197811106607</v>
@@ -14150,7 +14150,7 @@
         <v>807</v>
       </c>
       <c r="B808" t="n">
-        <v>0.1056820748357301</v>
+        <v>0.10568207483573</v>
       </c>
       <c r="C808" t="n">
         <v>0.1122933669826086</v>
@@ -14167,10 +14167,10 @@
         <v>808</v>
       </c>
       <c r="B809" t="n">
-        <v>0.1055727981677868</v>
+        <v>0.1055727981677867</v>
       </c>
       <c r="C809" t="n">
-        <v>0.1121803914135045</v>
+        <v>0.1121803914135044</v>
       </c>
       <c r="D809" t="n">
         <v>0.9640251317389542</v>
@@ -14575,7 +14575,7 @@
         <v>832</v>
       </c>
       <c r="B833" t="n">
-        <v>0.1030181647877065</v>
+        <v>0.1030181647877064</v>
       </c>
       <c r="C833" t="n">
         <v>0.109539225995344</v>
@@ -14748,7 +14748,7 @@
         <v>0.1019914878620394</v>
       </c>
       <c r="C843" t="n">
-        <v>0.1084779653287179</v>
+        <v>0.1084779653287178</v>
       </c>
       <c r="D843" t="n">
         <v>0.9651398459667613</v>
@@ -14816,7 +14816,7 @@
         <v>0.1015868809521673</v>
       </c>
       <c r="C847" t="n">
-        <v>0.1080597887349424</v>
+        <v>0.1080597887349423</v>
       </c>
       <c r="D847" t="n">
         <v>0.9651398459667613</v>
@@ -14915,7 +14915,7 @@
         <v>852</v>
       </c>
       <c r="B853" t="n">
-        <v>0.1009863736403719</v>
+        <v>0.1009863736403718</v>
       </c>
       <c r="C853" t="n">
         <v>0.1074392141485124</v>
@@ -15119,7 +15119,7 @@
         <v>864</v>
       </c>
       <c r="B865" t="n">
-        <v>0.0998080284255505</v>
+        <v>0.09980802842555048</v>
       </c>
       <c r="C865" t="n">
         <v>0.1062217711389839</v>
@@ -15170,7 +15170,7 @@
         <v>867</v>
       </c>
       <c r="B868" t="n">
-        <v>0.09951808869225449</v>
+        <v>0.09951808869225448</v>
       </c>
       <c r="C868" t="n">
         <v>0.1059222716094292</v>
@@ -15221,10 +15221,10 @@
         <v>870</v>
       </c>
       <c r="B871" t="n">
-        <v>0.09922998165696272</v>
+        <v>0.09922998165696269</v>
       </c>
       <c r="C871" t="n">
-        <v>0.1056246896972013</v>
+        <v>0.1056246896972012</v>
       </c>
       <c r="D871" t="n">
         <v>0.9654438589379813</v>
@@ -15238,10 +15238,10 @@
         <v>871</v>
       </c>
       <c r="B872" t="n">
-        <v>0.09913435103732832</v>
+        <v>0.0991343510373283</v>
       </c>
       <c r="C872" t="n">
-        <v>0.1055259195490484</v>
+        <v>0.1055259195490483</v>
       </c>
       <c r="D872" t="n">
         <v>0.9654438589379813</v>
@@ -15306,7 +15306,7 @@
         <v>875</v>
       </c>
       <c r="B876" t="n">
-        <v>0.09875384140890314</v>
+        <v>0.09875384140890313</v>
       </c>
       <c r="C876" t="n">
         <v>0.105132944947374</v>
@@ -15323,7 +15323,7 @@
         <v>876</v>
       </c>
       <c r="B877" t="n">
-        <v>0.09865921491186674</v>
+        <v>0.09865921491186672</v>
       </c>
       <c r="C877" t="n">
         <v>0.1050352253563863</v>
@@ -15340,7 +15340,7 @@
         <v>877</v>
       </c>
       <c r="B878" t="n">
-        <v>0.09856478786864725</v>
+        <v>0.09856478786864724</v>
       </c>
       <c r="C878" t="n">
         <v>0.1049377144222544</v>
@@ -15357,7 +15357,7 @@
         <v>878</v>
       </c>
       <c r="B879" t="n">
-        <v>0.09847055982999905</v>
+        <v>0.09847055982999904</v>
       </c>
       <c r="C879" t="n">
         <v>0.1048404116663234</v>
@@ -15377,7 +15377,7 @@
         <v>0.09837653035029227</v>
       </c>
       <c r="C880" t="n">
-        <v>0.1047433166130188</v>
+        <v>0.1047433166130187</v>
       </c>
       <c r="D880" t="n">
         <v>0.9654438589379813</v>
@@ -15391,10 +15391,10 @@
         <v>880</v>
       </c>
       <c r="B881" t="n">
-        <v>0.09828269898767737</v>
+        <v>0.09828269898767736</v>
       </c>
       <c r="C881" t="n">
-        <v>0.1046464287900514</v>
+        <v>0.1046464287900513</v>
       </c>
       <c r="D881" t="n">
         <v>0.9654438589379813</v>
@@ -15408,7 +15408,7 @@
         <v>881</v>
       </c>
       <c r="B882" t="n">
-        <v>0.09818906530424784</v>
+        <v>0.09818906530424783</v>
       </c>
       <c r="C882" t="n">
         <v>0.1045497477286198</v>
@@ -15425,7 +15425,7 @@
         <v>882</v>
       </c>
       <c r="B883" t="n">
-        <v>0.09809562886620121</v>
+        <v>0.0980956288662012</v>
       </c>
       <c r="C883" t="n">
         <v>0.1044532729636082</v>
@@ -15459,7 +15459,7 @@
         <v>884</v>
       </c>
       <c r="B885" t="n">
-        <v>0.09790934601251663</v>
+        <v>0.09790934601251662</v>
       </c>
       <c r="C885" t="n">
         <v>0.1042609404819759</v>
@@ -15510,7 +15510,7 @@
         <v>887</v>
       </c>
       <c r="B888" t="n">
-        <v>0.09763139048071488</v>
+        <v>0.0976313904807149</v>
       </c>
       <c r="C888" t="n">
         <v>0.1039739775880234</v>
@@ -15544,7 +15544,7 @@
         <v>889</v>
       </c>
       <c r="B890" t="n">
-        <v>0.09744706116530465</v>
+        <v>0.09744706116530462</v>
       </c>
       <c r="C890" t="n">
         <v>0.1037836877007876</v>
@@ -15595,7 +15595,7 @@
         <v>892</v>
       </c>
       <c r="B893" t="n">
-        <v>0.09717202079035685</v>
+        <v>0.09717202079035683</v>
       </c>
       <c r="C893" t="n">
         <v>0.1034997723047572</v>
@@ -15629,7 +15629,7 @@
         <v>894</v>
       </c>
       <c r="B895" t="n">
-        <v>0.09698962512164246</v>
+        <v>0.09698962512164247</v>
       </c>
       <c r="C895" t="n">
         <v>0.103311503452709</v>
@@ -15680,7 +15680,7 @@
         <v>897</v>
       </c>
       <c r="B898" t="n">
-        <v>0.09671747109354922</v>
+        <v>0.09671747109354921</v>
       </c>
       <c r="C898" t="n">
         <v>0.1030306042164106</v>
@@ -15697,7 +15697,7 @@
         <v>898</v>
       </c>
       <c r="B899" t="n">
-        <v>0.09662713551946639</v>
+        <v>0.09662713551946638</v>
       </c>
       <c r="C899" t="n">
         <v>0.1029373706544735</v>
@@ -15748,7 +15748,7 @@
         <v>901</v>
       </c>
       <c r="B902" t="n">
-        <v>0.0963572713164122</v>
+        <v>0.09635727131641218</v>
       </c>
       <c r="C902" t="n">
         <v>0.1026588632553668</v>
@@ -15765,7 +15765,7 @@
         <v>902</v>
       </c>
       <c r="B903" t="n">
-        <v>0.09626769632578437</v>
+        <v>0.09626769632578436</v>
       </c>
       <c r="C903" t="n">
         <v>0.1025664240084282</v>
@@ -15799,7 +15799,7 @@
         <v>904</v>
       </c>
       <c r="B905" t="n">
-        <v>0.09608911405805316</v>
+        <v>0.09608911405805315</v>
       </c>
       <c r="C905" t="n">
         <v>0.1023821382378651</v>
@@ -15833,7 +15833,7 @@
         <v>906</v>
       </c>
       <c r="B907" t="n">
-        <v>0.09591128672014956</v>
+        <v>0.09591128672014958</v>
       </c>
       <c r="C907" t="n">
         <v>0.1021986405179257</v>
@@ -15884,7 +15884,7 @@
         <v>909</v>
       </c>
       <c r="B910" t="n">
-        <v>0.09564595614698697</v>
+        <v>0.09564595614698695</v>
       </c>
       <c r="C910" t="n">
         <v>0.1019248658837885</v>
@@ -15901,7 +15901,7 @@
         <v>910</v>
       </c>
       <c r="B911" t="n">
-        <v>0.09555788763905385</v>
+        <v>0.09555788763905387</v>
       </c>
       <c r="C911" t="n">
         <v>0.1018339989580824</v>
@@ -15918,7 +15918,7 @@
         <v>911</v>
       </c>
       <c r="B912" t="n">
-        <v>0.09547000620252317</v>
+        <v>0.09547000620252315</v>
       </c>
       <c r="C912" t="n">
         <v>0.1017433271828419</v>
@@ -15986,7 +15986,7 @@
         <v>915</v>
       </c>
       <c r="B916" t="n">
-        <v>0.09512034625916908</v>
+        <v>0.09512034625916907</v>
       </c>
       <c r="C916" t="n">
         <v>0.1013825860135192</v>
@@ -16074,7 +16074,7 @@
         <v>0.09468745249781016</v>
       </c>
       <c r="C921" t="n">
-        <v>0.1009360185510603</v>
+        <v>0.1009360185510602</v>
       </c>
       <c r="D921" t="n">
         <v>0.9677746250506688</v>
@@ -16190,7 +16190,7 @@
         <v>927</v>
       </c>
       <c r="B928" t="n">
-        <v>0.09408916269436525</v>
+        <v>0.09408916269436524</v>
       </c>
       <c r="C928" t="n">
         <v>0.1003189102817676</v>
@@ -16224,7 +16224,7 @@
         <v>929</v>
       </c>
       <c r="B930" t="n">
-        <v>0.09391987917044496</v>
+        <v>0.09391987917044493</v>
       </c>
       <c r="C930" t="n">
         <v>0.1001443182989643</v>
@@ -16258,7 +16258,7 @@
         <v>931</v>
       </c>
       <c r="B932" t="n">
-        <v>0.09375132989395442</v>
+        <v>0.09375132989395439</v>
       </c>
       <c r="C932" t="n">
         <v>0.09997049043427779</v>
@@ -16278,7 +16278,7 @@
         <v>0.09366733031950827</v>
       </c>
       <c r="C933" t="n">
-        <v>0.09988386268941013</v>
+        <v>0.09988386268941012</v>
       </c>
       <c r="D933" t="n">
         <v>0.9677746250506688</v>
@@ -16295,7 +16295,7 @@
         <v>0.09358351398538105</v>
       </c>
       <c r="C934" t="n">
-        <v>0.09979742555930959</v>
+        <v>0.09979742555930958</v>
       </c>
       <c r="D934" t="n">
         <v>0.9677746250506688</v>
@@ -16309,7 +16309,7 @@
         <v>934</v>
       </c>
       <c r="B935" t="n">
-        <v>0.09349988079799139</v>
+        <v>0.09349988079799137</v>
       </c>
       <c r="C935" t="n">
         <v>0.0997111789194972</v>
@@ -16346,7 +16346,7 @@
         <v>0.09333316352053904</v>
       </c>
       <c r="C937" t="n">
-        <v>0.09953925664466415</v>
+        <v>0.09953925664466413</v>
       </c>
       <c r="D937" t="n">
         <v>0.9677746250506688</v>
@@ -16360,10 +16360,10 @@
         <v>937</v>
       </c>
       <c r="B938" t="n">
-        <v>0.09325007927434885</v>
+        <v>0.09325007927434883</v>
       </c>
       <c r="C938" t="n">
-        <v>0.0994535807921179</v>
+        <v>0.09945358079211788</v>
       </c>
       <c r="D938" t="n">
         <v>0.9677746250506688</v>
@@ -16380,7 +16380,7 @@
         <v>0.09316717786235448</v>
       </c>
       <c r="C939" t="n">
-        <v>0.09936809499451843</v>
+        <v>0.0993680949945184</v>
       </c>
       <c r="D939" t="n">
         <v>0.9677746250506688</v>
@@ -16394,7 +16394,7 @@
         <v>939</v>
       </c>
       <c r="B940" t="n">
-        <v>0.09308445922115006</v>
+        <v>0.09308445922115005</v>
       </c>
       <c r="C940" t="n">
         <v>0.09928279915794853</v>
@@ -16431,7 +16431,7 @@
         <v>0.09291957002522129</v>
       </c>
       <c r="C942" t="n">
-        <v>0.09911277702032474</v>
+        <v>0.09911277702032473</v>
       </c>
       <c r="D942" t="n">
         <v>0.9677746250506688</v>
@@ -16462,7 +16462,7 @@
         <v>943</v>
       </c>
       <c r="B944" t="n">
-        <v>0.09275541128785336</v>
+        <v>0.09275541128785335</v>
       </c>
       <c r="C944" t="n">
         <v>0.09894351373788123</v>
@@ -16479,10 +16479,10 @@
         <v>944</v>
       </c>
       <c r="B945" t="n">
-        <v>0.0926736057388054</v>
+        <v>0.09267360573880538</v>
       </c>
       <c r="C945" t="n">
-        <v>0.09885916648950541</v>
+        <v>0.09885916648950539</v>
       </c>
       <c r="D945" t="n">
         <v>0.9677746250506688</v>
@@ -16496,10 +16496,10 @@
         <v>945</v>
       </c>
       <c r="B946" t="n">
-        <v>0.09259198269118925</v>
+        <v>0.09259198269118926</v>
       </c>
       <c r="C946" t="n">
-        <v>0.09877500875122926</v>
+        <v>0.09877500875122924</v>
       </c>
       <c r="D946" t="n">
         <v>0.9677746250506688</v>
@@ -16513,7 +16513,7 @@
         <v>946</v>
       </c>
       <c r="B947" t="n">
-        <v>0.09251054211690368</v>
+        <v>0.09251054211690367</v>
       </c>
       <c r="C947" t="n">
         <v>0.09869104046493503</v>
@@ -16547,10 +16547,10 @@
         <v>948</v>
       </c>
       <c r="B949" t="n">
-        <v>0.09234820829704615</v>
+        <v>0.09234820829704614</v>
       </c>
       <c r="C949" t="n">
-        <v>0.09852367203730349</v>
+        <v>0.0985236720373035</v>
       </c>
       <c r="D949" t="n">
         <v>0.9677746250506688</v>
@@ -16584,7 +16584,7 @@
         <v>0.0921866041359211</v>
       </c>
       <c r="C951" t="n">
-        <v>0.09835706082460248</v>
+        <v>0.09835706082460247</v>
       </c>
       <c r="D951" t="n">
         <v>0.9677746250506688</v>
@@ -16598,7 +16598,7 @@
         <v>951</v>
       </c>
       <c r="B952" t="n">
-        <v>0.09210607564860085</v>
+        <v>0.09210607564860084</v>
       </c>
       <c r="C952" t="n">
         <v>0.09827403907080098</v>
@@ -16615,7 +16615,7 @@
         <v>952</v>
       </c>
       <c r="B953" t="n">
-        <v>0.09202572954800947</v>
+        <v>0.09202572954800946</v>
       </c>
       <c r="C953" t="n">
         <v>0.09819120650381168</v>
@@ -16632,7 +16632,7 @@
         <v>953</v>
       </c>
       <c r="B954" t="n">
-        <v>0.09194556583127537</v>
+        <v>0.09194556583127535</v>
       </c>
       <c r="C954" t="n">
         <v>0.09810856309127285</v>
@@ -16649,7 +16649,7 @@
         <v>954</v>
       </c>
       <c r="B955" t="n">
-        <v>0.09186558449819895</v>
+        <v>0.09186558449819894</v>
       </c>
       <c r="C955" t="n">
         <v>0.09802610880357908</v>
@@ -16686,7 +16686,7 @@
         <v>0.09170616899409598</v>
       </c>
       <c r="C957" t="n">
-        <v>0.09786176749661972</v>
+        <v>0.09786176749661971</v>
       </c>
       <c r="D957" t="n">
         <v>0.9683826509931091</v>
@@ -16734,7 +16734,7 @@
         <v>959</v>
       </c>
       <c r="B960" t="n">
-        <v>0.09146841373631197</v>
+        <v>0.09146841373631195</v>
       </c>
       <c r="C960" t="n">
         <v>0.0976166733635256</v>
@@ -16768,7 +16768,7 @@
         <v>961</v>
       </c>
       <c r="B962" t="n">
-        <v>0.09131082233765248</v>
+        <v>0.09131082233765245</v>
       </c>
       <c r="C962" t="n">
         <v>0.09745422226314636</v>
@@ -16788,7 +16788,7 @@
         <v>0.09123230030413033</v>
       </c>
       <c r="C963" t="n">
-        <v>0.09737328015718638</v>
+        <v>0.09737328015718637</v>
       </c>
       <c r="D963" t="n">
         <v>0.9687880016214026</v>
@@ -16805,7 +16805,7 @@
         <v>0.09115396073080112</v>
       </c>
       <c r="C964" t="n">
-        <v>0.09729252699236855</v>
+        <v>0.09729252699236854</v>
       </c>
       <c r="D964" t="n">
         <v>0.9687880016214026</v>
@@ -16819,10 +16819,10 @@
         <v>964</v>
       </c>
       <c r="B965" t="n">
-        <v>0.09107580363004812</v>
+        <v>0.09107580363004811</v>
       </c>
       <c r="C965" t="n">
-        <v>0.09721196275273759</v>
+        <v>0.09721196275273758</v>
       </c>
       <c r="D965" t="n">
         <v>0.9687880016214026</v>
@@ -16836,10 +16836,10 @@
         <v>965</v>
       </c>
       <c r="B966" t="n">
-        <v>0.09099782901404083</v>
+        <v>0.09099782901404081</v>
       </c>
       <c r="C966" t="n">
-        <v>0.09713158742225998</v>
+        <v>0.09713158742225997</v>
       </c>
       <c r="D966" t="n">
         <v>0.9687880016214026</v>
@@ -16853,10 +16853,10 @@
         <v>966</v>
       </c>
       <c r="B967" t="n">
-        <v>0.09092003689446074</v>
+        <v>0.09092003689446072</v>
       </c>
       <c r="C967" t="n">
-        <v>0.09705140098455585</v>
+        <v>0.09705140098455582</v>
       </c>
       <c r="D967" t="n">
         <v>0.9687880016214026</v>
@@ -16870,10 +16870,10 @@
         <v>967</v>
       </c>
       <c r="B968" t="n">
-        <v>0.09084242728222654</v>
+        <v>0.09084242728222652</v>
       </c>
       <c r="C968" t="n">
-        <v>0.09697140342263065</v>
+        <v>0.09697140342263064</v>
       </c>
       <c r="D968" t="n">
         <v>0.9687880016214026</v>
@@ -16890,7 +16890,7 @@
         <v>0.090765000187219</v>
       </c>
       <c r="C969" t="n">
-        <v>0.0968915947186067</v>
+        <v>0.09689159471860671</v>
       </c>
       <c r="D969" t="n">
         <v>0.9687880016214026</v>
@@ -16921,7 +16921,7 @@
         <v>970</v>
       </c>
       <c r="B971" t="n">
-        <v>0.09061069358156837</v>
+        <v>0.09061069358156836</v>
       </c>
       <c r="C971" t="n">
         <v>0.09673254380672701</v>
@@ -16941,7 +16941,7 @@
         <v>0.09053381408302497</v>
       </c>
       <c r="C972" t="n">
-        <v>0.09665330155628891</v>
+        <v>0.0966533015562889</v>
       </c>
       <c r="D972" t="n">
         <v>0.9689906769355493</v>
@@ -16958,7 +16958,7 @@
         <v>0.09045711712536116</v>
       </c>
       <c r="C973" t="n">
-        <v>0.09657424807805495</v>
+        <v>0.09657424807805493</v>
       </c>
       <c r="D973" t="n">
         <v>0.9689906769355493</v>
@@ -16992,7 +16992,7 @@
         <v>0.09030427083231725</v>
       </c>
       <c r="C975" t="n">
-        <v>0.09641670733051642</v>
+        <v>0.0964167073305164</v>
       </c>
       <c r="D975" t="n">
         <v>0.9689906769355493</v>
@@ -17006,7 +17006,7 @@
         <v>975</v>
       </c>
       <c r="B976" t="n">
-        <v>0.09022812148980495</v>
+        <v>0.09022812148980493</v>
       </c>
       <c r="C976" t="n">
         <v>0.09633822000091548</v>
@@ -17023,10 +17023,10 @@
         <v>976</v>
       </c>
       <c r="B977" t="n">
-        <v>0.09015215467337531</v>
+        <v>0.0901521546733753</v>
       </c>
       <c r="C977" t="n">
-        <v>0.09625992132240807</v>
+        <v>0.09625992132240806</v>
       </c>
       <c r="D977" t="n">
         <v>0.9688893392784759</v>
@@ -17077,7 +17077,7 @@
         <v>0.08992534924453782</v>
       </c>
       <c r="C980" t="n">
-        <v>0.09602615679804988</v>
+        <v>0.09602615679804985</v>
       </c>
       <c r="D980" t="n">
         <v>0.9688893392784759</v>
@@ -17108,7 +17108,7 @@
         <v>981</v>
       </c>
       <c r="B982" t="n">
-        <v>0.08977505793660198</v>
+        <v>0.08977505793660197</v>
       </c>
       <c r="C982" t="n">
         <v>0.09587125624676573</v>
@@ -17125,10 +17125,10 @@
         <v>982</v>
       </c>
       <c r="B983" t="n">
-        <v>0.0897001858912754</v>
+        <v>0.08970018589127539</v>
       </c>
       <c r="C983" t="n">
-        <v>0.09579408855057474</v>
+        <v>0.09579408855057471</v>
       </c>
       <c r="D983" t="n">
         <v>0.9688893392784759</v>
@@ -17142,10 +17142,10 @@
         <v>983</v>
       </c>
       <c r="B984" t="n">
-        <v>0.08962549620290135</v>
+        <v>0.08962549620290133</v>
       </c>
       <c r="C984" t="n">
-        <v>0.09571710915901331</v>
+        <v>0.09571710915901328</v>
       </c>
       <c r="D984" t="n">
         <v>0.9688893392784759</v>
@@ -17159,10 +17159,10 @@
         <v>984</v>
       </c>
       <c r="B985" t="n">
-        <v>0.08955098882842824</v>
+        <v>0.08955098882842823</v>
       </c>
       <c r="C985" t="n">
-        <v>0.09564031800471809</v>
+        <v>0.09564031800471808</v>
       </c>
       <c r="D985" t="n">
         <v>0.9687880016214026</v>
@@ -17213,7 +17213,7 @@
         <v>0.08932856007507275</v>
       </c>
       <c r="C988" t="n">
-        <v>0.09541107321315614</v>
+        <v>0.09541107321315613</v>
       </c>
       <c r="D988" t="n">
         <v>0.9688893392784759</v>
@@ -17261,7 +17261,7 @@
         <v>990</v>
       </c>
       <c r="B991" t="n">
-        <v>0.08910777005038244</v>
+        <v>0.08910777005038242</v>
       </c>
       <c r="C991" t="n">
         <v>0.09518351961260746</v>
@@ -17295,10 +17295,10 @@
         <v>992</v>
       </c>
       <c r="B993" t="n">
-        <v>0.08896148607335311</v>
+        <v>0.08896148607335309</v>
       </c>
       <c r="C993" t="n">
-        <v>0.09503275542903185</v>
+        <v>0.09503275542903183</v>
       </c>
       <c r="D993" t="n">
         <v>0.9689906769355493</v>
@@ -17312,10 +17312,10 @@
         <v>993</v>
       </c>
       <c r="B994" t="n">
-        <v>0.08888861661909608</v>
+        <v>0.08888861661909606</v>
       </c>
       <c r="C994" t="n">
-        <v>0.09495765445894729</v>
+        <v>0.09495765445894726</v>
       </c>
       <c r="D994" t="n">
         <v>0.9689906769355493</v>
@@ -17329,7 +17329,7 @@
         <v>994</v>
       </c>
       <c r="B995" t="n">
-        <v>0.08881592871444412</v>
+        <v>0.0888159287144441</v>
       </c>
       <c r="C995" t="n">
         <v>0.09488274073496386</v>
@@ -17349,7 +17349,7 @@
         <v>0.08874342224527389</v>
       </c>
       <c r="C996" t="n">
-        <v>0.09480801412202466</v>
+        <v>0.09480801412202465</v>
       </c>
       <c r="D996" t="n">
         <v>0.9691933522496959</v>
@@ -17366,7 +17366,7 @@
         <v>0.08867109708991233</v>
       </c>
       <c r="C997" t="n">
-        <v>0.09473347447786218</v>
+        <v>0.09473347447786216</v>
       </c>
       <c r="D997" t="n">
         <v>0.9689906769355493</v>
@@ -17383,7 +17383,7 @@
         <v>0.08859895311898629</v>
       </c>
       <c r="C998" t="n">
-        <v>0.09465912165285233</v>
+        <v>0.09465912165285231</v>
       </c>
       <c r="D998" t="n">
         <v>0.9689906769355493</v>
@@ -17397,10 +17397,10 @@
         <v>998</v>
       </c>
       <c r="B999" t="n">
-        <v>0.08852699019527986</v>
+        <v>0.08852699019527983</v>
       </c>
       <c r="C999" t="n">
-        <v>0.09458495548987572</v>
+        <v>0.09458495548987571</v>
       </c>
       <c r="D999" t="n">
         <v>0.9691933522496959</v>
@@ -17414,7 +17414,7 @@
         <v>999</v>
       </c>
       <c r="B1000" t="n">
-        <v>0.08845520817359945</v>
+        <v>0.08845520817359943</v>
       </c>
       <c r="C1000" t="n">
         <v>0.09451097582418659</v>
@@ -17431,10 +17431,10 @@
         <v>1000</v>
       </c>
       <c r="B1001" t="n">
-        <v>0.08838360690064685</v>
+        <v>0.08838360690064684</v>
       </c>
       <c r="C1001" t="n">
-        <v>0.09443718248328919</v>
+        <v>0.09443718248328918</v>
       </c>
       <c r="D1001" t="n">
         <v>0.9691933522496959</v>
